--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484377_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484377_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0295</v>
+        <v>4.946</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2296</v>
+        <v>2.3913</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7999</v>
+        <v>2.5547</v>
       </c>
       <c r="G2" t="n">
         <v>2.2757</v>
@@ -610,13 +610,13 @@
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6839</v>
+        <v>0.6004</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3548</v>
+        <v>-0.1931</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0387</v>
+        <v>0.7936</v>
       </c>
       <c r="V2" t="n">
         <v>3.0466</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7855</v>
+        <v>4.0807</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0966</v>
+        <v>0.8345</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6889</v>
+        <v>3.2462</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9572</v>
+        <v>2.4271</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1773</v>
+        <v>-0.2576</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7799</v>
+        <v>2.6848</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0566</v>
+        <v>2.0518</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3548</v>
+        <v>0.9849</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7017</v>
+        <v>1.0669</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0994</v>
+        <v>0.3753</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1775</v>
+        <v>-1.2425</v>
       </c>
       <c r="O3" t="n">
-        <v>1.0782</v>
+        <v>1.6178</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9101</v>
+        <v>-0.0069</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4074</v>
+        <v>-0.2406</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5028</v>
+        <v>0.2337</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2772</v>
+        <v>1.6604</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2772</v>
+        <v>1.6604</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4911</v>
+        <v>2.887</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5717</v>
+        <v>1.3887</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9194</v>
+        <v>1.4983</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4271</v>
+        <v>2.9572</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2576</v>
+        <v>1.1773</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6848</v>
+        <v>1.7799</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0518</v>
+        <v>3.0566</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9849</v>
+        <v>2.3548</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0669</v>
+        <v>0.7017</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3753</v>
+        <v>-0.0994</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2425</v>
+        <v>-1.1775</v>
       </c>
       <c r="O4" t="n">
-        <v>1.6178</v>
+        <v>1.0782</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>-1.3674</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5965</v>
+        <v>0.0117</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5034</v>
+        <v>-0.3004</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0931</v>
+        <v>0.3121</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6604</v>
+        <v>-0.2772</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.6604</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4027</v>
+        <v>1.7008</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.433</v>
+        <v>0.1073</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8357</v>
+        <v>1.5935</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3384</v>
+        <v>1.5324</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1614</v>
+        <v>1.2628</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4998</v>
+        <v>0.2696</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3157</v>
+        <v>0.3287</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8161</v>
+        <v>1.0028</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5004</v>
+        <v>-0.6741</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6541</v>
+        <v>1.2037</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.2599</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.9437</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.119</v>
+        <v>0.055</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2105</v>
+        <v>-0.2214</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0915</v>
+        <v>0.2764</v>
       </c>
       <c r="V5" t="n">
-        <v>2.16</v>
+        <v>-0.2772</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2772</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3863</v>
+        <v>1.5815</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8359</v>
+        <v>-0.9274</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2222</v>
+        <v>2.5089</v>
       </c>
       <c r="G6" t="n">
-        <v>1.164</v>
+        <v>0.3384</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2315</v>
+        <v>-0.1614</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0675</v>
+        <v>0.4998</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1284</v>
+        <v>-0.3157</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2742</v>
+        <v>-0.8161</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1459</v>
+        <v>0.5004</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0357</v>
+        <v>0.6541</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0427</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>1.0784</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>-2.3441</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0036</v>
+        <v>0.0598</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0108</v>
+        <v>-0.7049</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0145</v>
+        <v>0.7647</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3793</v>
+        <v>1.3625</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1863</v>
+        <v>-1.5452</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5656</v>
+        <v>2.9077</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0973</v>
+        <v>0.4579</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0975</v>
+        <v>1.3469</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0002</v>
+        <v>-0.8891</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6319</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0422</v>
+        <v>0.7572</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6741</v>
+        <v>-1.4281</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7292</v>
+        <v>1.1288</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0553</v>
+        <v>0.5897</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.5391</v>
       </c>
       <c r="P7" t="n">
-        <v>0.586</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R7" t="n">
         <v>0.7814</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2454</v>
+        <v>0.4711</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5777</v>
+        <v>-0.1395</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3322</v>
+        <v>0.6107</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9414</v>
+        <v>1.6056</v>
       </c>
       <c r="W7" t="n">
         <v>1.2186</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>M. LLUCIÀ MONSÓ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2474</v>
+        <v>1.3248</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1555</v>
+        <v>-0.1863</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4029</v>
+        <v>1.5111</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5324</v>
+        <v>0.0973</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2628</v>
+        <v>0.0975</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2696</v>
+        <v>-0.0002</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3287</v>
+        <v>-0.6319</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0028</v>
+        <v>0.0422</v>
       </c>
       <c r="L8" t="n">
         <v>-0.6741</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2037</v>
+        <v>0.7292</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2599</v>
+        <v>0.0553</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9437</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3984</v>
+        <v>-0.2999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4842</v>
+        <v>-0.5777</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0858</v>
+        <v>0.2778</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>0.9414</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
         <v>-0.2772</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0763</v>
+        <v>1.2562</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5046</v>
+        <v>-0.7754</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5809</v>
+        <v>2.0315</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4579</v>
+        <v>1.164</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3469</v>
+        <v>1.2315</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8891</v>
+        <v>-0.0675</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6709000000000001</v>
+        <v>1.1284</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7572</v>
+        <v>2.2742</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4281</v>
+        <v>-1.1459</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1288</v>
+        <v>0.0357</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5897</v>
+        <v>-1.0427</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5391</v>
+        <v>1.0784</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1721</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1849</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0989</v>
+        <v>0.0497</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2838</v>
+        <v>0.8238</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6056</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3711</v>
+        <v>0.0599</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6186</v>
+        <v>-1.8209</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9897</v>
+        <v>1.8808</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9937</v>
@@ -1234,13 +1234,13 @@
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3648</v>
+        <v>0.0536</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0246</v>
+        <v>-0.2269</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3894</v>
+        <v>0.2805</v>
       </c>
       <c r="V10" t="n">
         <v>0.6093</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.1646</v>
       </c>
       <c r="E11" t="n">
         <v>-1.2312</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6309</v>
+        <v>1.0666</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0732</v>
@@ -1312,13 +1312,13 @@
         <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.422</v>
+        <v>0.0138</v>
       </c>
       <c r="T11" t="n">
         <v>-0.341</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.081</v>
+        <v>0.3548</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2772</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9897</v>
+        <v>-1.1531</v>
       </c>
       <c r="E12" t="n">
         <v>-1.3786</v>
       </c>
       <c r="F12" t="n">
-        <v>0.389</v>
+        <v>0.2256</v>
       </c>
       <c r="G12" t="n">
         <v>0.2582</v>
@@ -1390,13 +1390,13 @@
         <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2246</v>
+        <v>-0.388</v>
       </c>
       <c r="T12" t="n">
         <v>-0.652</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4274</v>
+        <v>0.264</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2186</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.5792</v>
+        <v>17.8817</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.4458</v>
+        <v>-3.1432</v>
       </c>
       <c r="F13" t="n">
-        <v>21.0251</v>
+        <v>21.0249</v>
       </c>
       <c r="G13" t="n">
         <v>9.4413</v>
       </c>
       <c r="H13" t="n">
-        <v>4.718799999999999</v>
+        <v>4.7188</v>
       </c>
       <c r="I13" t="n">
         <v>4.7225</v>
@@ -1453,7 +1453,7 @@
         <v>5.147100000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.9391</v>
+        <v>-2.939099999999999</v>
       </c>
       <c r="O13" t="n">
         <v>8.0863</v>
@@ -1468,22 +1468,22 @@
         <v>11.7206</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1414</v>
+        <v>1.444100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.8505</v>
+        <v>-3.547800000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>4.991999999999999</v>
+        <v>4.9921</v>
       </c>
       <c r="V13" t="n">
         <v>7.973099999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>8.807600000000001</v>
+        <v>8.807599999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8345</v>
+        <v>-0.8344999999999998</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0581</v>
+        <v>1.3471</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4594</v>
+        <v>-1.3583</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5175</v>
+        <v>2.7055</v>
       </c>
       <c r="G14" t="n">
         <v>2.2417</v>
@@ -1546,13 +1546,13 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1288</v>
+        <v>0.1603</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.839</v>
+        <v>-0.7379</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.8981</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6642</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9195</v>
+        <v>1.2681</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5787</v>
+        <v>-0.1743</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4982</v>
+        <v>1.4424</v>
       </c>
       <c r="G15" t="n">
         <v>1.6071</v>
@@ -1624,13 +1624,13 @@
         <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0269</v>
+        <v>0.3756</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.4429</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8742</v>
+        <v>0.8184</v>
       </c>
       <c r="V15" t="n">
         <v>-1.4959</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4385</v>
+        <v>-0.3397</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0012</v>
+        <v>-0.538</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4396</v>
+        <v>0.1984</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1981</v>
+        <v>0.9211</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.24</v>
+        <v>0.2336</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9581</v>
+        <v>0.6875</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1408</v>
+        <v>2.2344</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4119</v>
+        <v>1.6807</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5527</v>
+        <v>0.5537</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0573</v>
+        <v>-1.3133</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6518</v>
+        <v>-1.4472</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4054</v>
+        <v>0.1338</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5876</v>
+        <v>-0.4794</v>
       </c>
       <c r="T16" t="n">
-        <v>1.142</v>
+        <v>-0.819</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4456</v>
+        <v>0.3397</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0229</v>
+        <v>-1.3774</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8414</v>
+        <v>-0.0931</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1816</v>
+        <v>-1.2843</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9211</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2336</v>
+        <v>1.3761</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6875</v>
+        <v>-0.7294</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2344</v>
+        <v>2.0303</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6807</v>
+        <v>2.6234</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5537</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3133</v>
+        <v>-1.3836</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4472</v>
+        <v>-1.2474</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1338</v>
+        <v>-0.1362</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1627</v>
+        <v>0.3508</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1224</v>
+        <v>-0.4276</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0403</v>
+        <v>0.7784</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-3.1563</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.719</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4042</v>
+        <v>-1.4173</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3684</v>
+        <v>-0.1111</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9641999999999999</v>
+        <v>-1.3062</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.1547</v>
+        <v>-2.1981</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8465</v>
+        <v>-1.24</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3081</v>
+        <v>-0.9581</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.6741</v>
+        <v>-0.1408</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6923</v>
+        <v>0.4119</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9818</v>
+        <v>-0.5527</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5195</v>
+        <v>-2.0573</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1542</v>
+        <v>-1.6518</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6737</v>
+        <v>-0.4054</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8519</v>
+        <v>0.6088</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7513</v>
+        <v>0.0297</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1006</v>
+        <v>0.579</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6642</v>
+        <v>-0.6093</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>P. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9582</v>
+        <v>-1.8537</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2953</v>
+        <v>-4.83</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6629</v>
+        <v>2.9763</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6467000000000001</v>
+        <v>-1.6185</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3761</v>
+        <v>-1.7263</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7294</v>
+        <v>0.1078</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0303</v>
+        <v>-2.2728</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6234</v>
+        <v>-1.5721</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.7007</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3836</v>
+        <v>0.6543</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2474</v>
+        <v>-0.1542</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1362</v>
+        <v>0.8085</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.23</v>
+        <v>0.1555</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6299</v>
+        <v>-0.6038</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3999</v>
+        <v>0.7592</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.1563</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.719</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. EXPOSITO CORTS</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2944</v>
+        <v>-1.8812</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3156</v>
+        <v>-3.2784</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0212</v>
+        <v>1.3972</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3435</v>
+        <v>-3.1547</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9486</v>
+        <v>-1.8465</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2921</v>
+        <v>-1.3081</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6731</v>
+        <v>-3.6741</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0233</v>
+        <v>-1.6923</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.6964</v>
+        <v>-1.9818</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3296</v>
+        <v>0.5195</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0747</v>
+        <v>-0.1542</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4043</v>
+        <v>0.6737</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5601</v>
+        <v>0.3749</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6657</v>
+        <v>-0.1587</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1056</v>
+        <v>0.5336</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ROIG GARCIA</t>
+          <t>I. EXPOSITO CORTS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9479</v>
+        <v>-2.0843</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.4367</v>
+        <v>-3.2145</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4888</v>
+        <v>1.1301</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6185</v>
+        <v>-1.3435</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7263</v>
+        <v>0.9486</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1078</v>
+        <v>-2.2921</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.2728</v>
+        <v>-1.6731</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5721</v>
+        <v>1.0233</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7007</v>
+        <v>-2.6964</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6543</v>
+        <v>0.3296</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1542</v>
+        <v>-0.0747</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8085</v>
+        <v>0.4043</v>
       </c>
       <c r="P21" t="n">
         <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9387</v>
+        <v>-0.3501</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2105</v>
+        <v>-0.5646</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2717</v>
+        <v>0.2145</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3833</v>
+        <v>-3.5947</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9411</v>
+        <v>-2.0422</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4423</v>
+        <v>-1.5526</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4852</v>
@@ -2170,13 +2170,13 @@
         <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>0.153</v>
+        <v>-0.0584</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3878</v>
+        <v>-0.4889</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5407</v>
+        <v>0.4304</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6604</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1073</v>
+        <v>-5.6239</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7896</v>
+        <v>-5.3852</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3177</v>
+        <v>-0.2387</v>
       </c>
       <c r="G23" t="n">
         <v>-5.0578</v>
@@ -2248,13 +2248,13 @@
         <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7407</v>
+        <v>-0.2572</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1829</v>
+        <v>-0.7784</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4422</v>
+        <v>0.5212</v>
       </c>
       <c r="V23" t="n">
         <v>0.2772</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.5791</v>
+        <v>-15.557</v>
       </c>
       <c r="E24" t="n">
-        <v>-21.025</v>
+        <v>-21.0251</v>
       </c>
       <c r="F24" t="n">
-        <v>3.4458</v>
+        <v>5.4681</v>
       </c>
       <c r="G24" t="n">
         <v>-9.4412</v>
@@ -2314,7 +2314,7 @@
         <v>-7.657800000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>3.363600000000001</v>
+        <v>3.3636</v>
       </c>
       <c r="P24" t="n">
         <v>0.9767</v>
@@ -2326,13 +2326,13 @@
         <v>12.6972</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1416</v>
+        <v>0.8807999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.9922</v>
+        <v>-4.992100000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>3.8504</v>
+        <v>5.8725</v>
       </c>
       <c r="V24" t="n">
         <v>-7.9731</v>
@@ -2341,7 +2341,7 @@
         <v>0.8347</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.807600000000001</v>
+        <v>-8.807599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484377_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484377_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,45 +714,50 @@
       </c>
       <c r="X3" t="n">
         <v>1.6604</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.887</v>
+        <v>1.966</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3887</v>
+        <v>0.4678</v>
       </c>
       <c r="F4" t="n">
         <v>1.4983</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9572</v>
+        <v>2.0362</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1773</v>
+        <v>0.2563</v>
       </c>
       <c r="I4" t="n">
         <v>1.7799</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0566</v>
+        <v>2.1356</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3548</v>
+        <v>1.4339</v>
       </c>
       <c r="L4" t="n">
         <v>0.7017</v>
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -792,7 +812,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -860,6 +880,11 @@
       </c>
       <c r="X5" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -870,7 +895,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -938,6 +963,11 @@
       </c>
       <c r="X6" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -948,7 +978,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1016,17 +1046,22 @@
       </c>
       <c r="X7" t="n">
         <v>0.3869</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. LLUCIÀ MONSÓ</t>
+          <t>M. LLUCIA MONSO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1094,45 +1129,50 @@
       </c>
       <c r="X8" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2562</v>
+        <v>0.9492</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7754</v>
+        <v>-1.0824</v>
       </c>
       <c r="F9" t="n">
         <v>2.0315</v>
       </c>
       <c r="G9" t="n">
-        <v>1.164</v>
+        <v>0.857</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2315</v>
+        <v>0.9245</v>
       </c>
       <c r="I9" t="n">
         <v>-0.0675</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1284</v>
+        <v>0.8214</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2742</v>
+        <v>1.9672</v>
       </c>
       <c r="L9" t="n">
         <v>-1.1459</v>
@@ -1172,480 +1212,511 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0599</v>
+        <v>0.921</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8209</v>
+        <v>0.921</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8808</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9937</v>
+        <v>0.921</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6273</v>
+        <v>0.921</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3085</v>
+        <v>0.921</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4032</v>
+        <v>0.921</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09470000000000001</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3148</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2241</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5389</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0536</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2269</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2805</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1646</v>
+        <v>0.307</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2312</v>
+        <v>0.307</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0666</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0732</v>
+        <v>0.307</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9353</v>
+        <v>0.307</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0085</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4995</v>
+        <v>0.307</v>
       </c>
       <c r="K11" t="n">
-        <v>2.0478</v>
+        <v>0.307</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5474</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5737</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1125</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5389</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0138</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.341</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3548</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. POCULL DURAN</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1531</v>
+        <v>0.0599</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3786</v>
+        <v>-1.8209</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2256</v>
+        <v>1.8808</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2582</v>
+        <v>-0.9937</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8608</v>
+        <v>-1.6273</v>
       </c>
       <c r="I12" t="n">
-        <v>1.119</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5313</v>
+        <v>-1.3085</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5718</v>
+        <v>-1.4032</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0405</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7895</v>
+        <v>0.3148</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2891</v>
+        <v>-0.2241</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0786</v>
+        <v>0.5389</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.388</v>
+        <v>0.0536</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.652</v>
+        <v>-0.2269</v>
       </c>
       <c r="U12" t="n">
-        <v>0.264</v>
+        <v>0.2805</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2186</v>
+        <v>0.6093</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.8817</v>
+        <v>-0.1646</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.1432</v>
+        <v>-1.2312</v>
       </c>
       <c r="F13" t="n">
-        <v>21.0249</v>
+        <v>1.0666</v>
       </c>
       <c r="G13" t="n">
-        <v>9.4413</v>
+        <v>-1.0732</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7188</v>
+        <v>0.9353</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7225</v>
+        <v>-2.0085</v>
       </c>
       <c r="J13" t="n">
-        <v>4.294300000000001</v>
+        <v>-0.4995</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6577</v>
+        <v>2.0478</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.3637</v>
+        <v>-2.5474</v>
       </c>
       <c r="M13" t="n">
-        <v>5.147100000000001</v>
+        <v>-0.5737</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.939099999999999</v>
+        <v>-1.1125</v>
       </c>
       <c r="O13" t="n">
-        <v>8.0863</v>
+        <v>0.5389</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9767999999999999</v>
+        <v>1.1721</v>
       </c>
       <c r="Q13" t="n">
-        <v>-12.6972</v>
+        <v>-0.3907</v>
       </c>
       <c r="R13" t="n">
-        <v>11.7206</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>1.444100000000001</v>
+        <v>0.0138</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.547800000000001</v>
+        <v>-0.341</v>
       </c>
       <c r="U13" t="n">
-        <v>4.9921</v>
+        <v>0.3548</v>
       </c>
       <c r="V13" t="n">
-        <v>7.973099999999999</v>
+        <v>-0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>8.807599999999999</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8344999999999998</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>L. POCULL DURAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3471</v>
+        <v>-1.1531</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.3583</v>
+        <v>-1.3786</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7055</v>
+        <v>0.2256</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2417</v>
+        <v>0.2582</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5275</v>
+        <v>-0.8608</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7141999999999999</v>
+        <v>1.119</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7785</v>
+        <v>-0.5313</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4121</v>
+        <v>-0.5718</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4632</v>
+        <v>0.7895</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1154</v>
+        <v>-0.2891</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3478</v>
+        <v>1.0786</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1603</v>
+        <v>-0.388</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7379</v>
+        <v>-0.652</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8981</v>
+        <v>0.264</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6642</v>
+        <v>-1.2186</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MERI RIUS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2681</v>
+        <v>17.8817</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1743</v>
+        <v>-3.1431</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4424</v>
+        <v>21.0249</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6071</v>
+        <v>9.4413</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3937</v>
+        <v>4.7188</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2134</v>
+        <v>4.7225</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2686</v>
+        <v>4.294300000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2686</v>
+        <v>7.657800000000002</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-3.3637</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3385</v>
+        <v>5.147100000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1251</v>
+        <v>-2.939099999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2134</v>
+        <v>8.0863</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>-0.9767999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-12.6972</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7814</v>
+        <v>11.7206</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3756</v>
+        <v>1.444100000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4429</v>
+        <v>-3.547800000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8184</v>
+        <v>4.9921</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4959</v>
+        <v>7.973099999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>8.807599999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
-      </c>
+        <v>-0.8344999999999998</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>A. MERI RIUS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3397</v>
+        <v>1.2681</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.538</v>
+        <v>-0.1743</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1984</v>
+        <v>1.4424</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9211</v>
+        <v>1.6071</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2336</v>
+        <v>0.3937</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6875</v>
+        <v>1.2134</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2344</v>
+        <v>0.2686</v>
       </c>
       <c r="K16" t="n">
-        <v>1.6807</v>
+        <v>0.2686</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5537</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3133</v>
+        <v>1.3385</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4472</v>
+        <v>0.1251</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1338</v>
+        <v>1.2134</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4794</v>
+        <v>0.3756</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.819</v>
+        <v>-0.4429</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3397</v>
+        <v>0.8184</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3774</v>
+        <v>1.0402</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0931</v>
+        <v>-1.6653</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2843</v>
+        <v>2.7055</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6467000000000001</v>
+        <v>1.9347</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3761</v>
+        <v>1.2206</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7294</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0303</v>
+        <v>0.4715</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6234</v>
+        <v>1.1051</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3836</v>
+        <v>1.4632</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2474</v>
+        <v>0.1154</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1362</v>
+        <v>1.3478</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3508</v>
+        <v>0.1603</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4276</v>
+        <v>-0.7379</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7784</v>
+        <v>0.8981</v>
       </c>
       <c r="V17" t="n">
-        <v>-3.1563</v>
+        <v>-0.6642</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.719</v>
+        <v>0.5545</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4373</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>M. SELLARÈS GIRALT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4173</v>
+        <v>0.307</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1111</v>
+        <v>0.307</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3062</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1981</v>
+        <v>0.307</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.24</v>
+        <v>0.307</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9581</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1408</v>
+        <v>0.307</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4119</v>
+        <v>0.307</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5527</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0573</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6518</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4054</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6088</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0297</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ROIG GARCIA</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8537</v>
+        <v>-0.3397</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.83</v>
+        <v>-0.538</v>
       </c>
       <c r="F19" t="n">
-        <v>2.9763</v>
+        <v>0.1984</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6185</v>
+        <v>0.9211</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7263</v>
+        <v>0.2336</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1078</v>
+        <v>0.6875</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.2728</v>
+        <v>2.2344</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5721</v>
+        <v>1.6807</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7007</v>
+        <v>0.5537</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6543</v>
+        <v>-1.3133</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1542</v>
+        <v>-1.4472</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8085</v>
+        <v>0.1338</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3907</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1555</v>
+        <v>-0.4794</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6038</v>
+        <v>-0.819</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7592</v>
+        <v>0.3397</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8812</v>
+        <v>-1.3774</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2784</v>
+        <v>-0.0931</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3972</v>
+        <v>-1.2843</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.1547</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8465</v>
+        <v>1.3761</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3081</v>
+        <v>-0.7294</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.6741</v>
+        <v>2.0303</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6923</v>
+        <v>2.6234</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9818</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5195</v>
+        <v>-1.3836</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1542</v>
+        <v>-1.2474</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6737</v>
+        <v>-0.1362</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3749</v>
+        <v>0.3508</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1587</v>
+        <v>-0.4276</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5336</v>
+        <v>0.7784</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6642</v>
+        <v>-3.1563</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5545</v>
+        <v>-0.719</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. EXPOSITO CORTS</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0843</v>
+        <v>-1.4173</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2145</v>
+        <v>-0.1111</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1301</v>
+        <v>-1.3062</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3435</v>
+        <v>-2.1981</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9486</v>
+        <v>-1.24</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2921</v>
+        <v>-0.9581</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6731</v>
+        <v>-0.1408</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0233</v>
+        <v>0.4119</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.6964</v>
+        <v>-0.5527</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3296</v>
+        <v>-2.0573</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0747</v>
+        <v>-1.6518</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4043</v>
+        <v>-0.4054</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3501</v>
+        <v>0.6088</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5646</v>
+        <v>0.0297</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2145</v>
+        <v>0.579</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>P. ROIG GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2226,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5947</v>
+        <v>-1.8537</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0422</v>
+        <v>-4.83</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5526</v>
+        <v>2.9763</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4852</v>
+        <v>-1.6185</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.229</v>
+        <v>-1.7263</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2562</v>
+        <v>0.1078</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2326</v>
+        <v>-2.2728</v>
       </c>
       <c r="K22" t="n">
-        <v>0.353</v>
+        <v>-1.5721</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1204</v>
+        <v>-0.7007</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.7178</v>
+        <v>0.6543</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.582</v>
+        <v>-0.1542</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1358</v>
+        <v>0.8085</v>
       </c>
       <c r="P22" t="n">
         <v>-0.3907</v>
@@ -2170,28 +2271,33 @@
         <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0584</v>
+        <v>0.1555</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4889</v>
+        <v>-0.6038</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4304</v>
+        <v>0.7592</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6604</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1675</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6239</v>
+        <v>-1.8812</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3852</v>
+        <v>-3.2784</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2387</v>
+        <v>1.3972</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.0578</v>
+        <v>-3.1547</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.1564</v>
+        <v>-1.8465</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9015</v>
+        <v>-1.3081</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.9305</v>
+        <v>-3.6741</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5695</v>
+        <v>-1.6923</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.361</v>
+        <v>-1.9818</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1273</v>
+        <v>0.5195</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5868</v>
+        <v>-0.1542</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5405</v>
+        <v>0.6737</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2572</v>
+        <v>0.3749</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7784</v>
+        <v>-0.1587</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5212</v>
+        <v>0.5336</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2772</v>
+        <v>0.5545</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. EXPOSITO CORTS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,318 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.557</v>
+        <v>-2.0843</v>
       </c>
       <c r="E24" t="n">
+        <v>-3.2145</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.1301</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.3435</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.9486</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-2.2921</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.6731</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.0233</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-2.6964</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.0747</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.3501</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.5646</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.2145</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A. BARQUETS ARIZA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-3.5947</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.0422</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.5526</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.4852</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.229</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.2562</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.2326</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.1204</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.7178</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.582</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.1358</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.0584</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.4889</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.4304</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.6604</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M. SEGARRA BAQUES</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-5.6239</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-5.3852</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.2387</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-5.0578</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-3.1564</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.9015</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.9305</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.5695</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.361</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.1273</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.5868</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.5405</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.2572</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.7784</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484377_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-15.5569</v>
+      </c>
+      <c r="E27" t="n">
         <v>-21.0251</v>
       </c>
-      <c r="F24" t="n">
-        <v>5.4681</v>
-      </c>
-      <c r="G24" t="n">
+      <c r="F27" t="n">
+        <v>5.468100000000002</v>
+      </c>
+      <c r="G27" t="n">
         <v>-9.4412</v>
       </c>
-      <c r="H24" t="n">
-        <v>-4.7187</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H27" t="n">
+        <v>-4.7186</v>
+      </c>
+      <c r="I27" t="n">
         <v>-4.7225</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J27" t="n">
         <v>-5.1469</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K27" t="n">
         <v>2.9391</v>
       </c>
-      <c r="L24" t="n">
-        <v>-8.0861</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="L27" t="n">
+        <v>-8.086100000000002</v>
+      </c>
+      <c r="M27" t="n">
         <v>-4.2942</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N27" t="n">
         <v>-7.657800000000001</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O27" t="n">
         <v>3.3636</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P27" t="n">
         <v>0.9767</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q27" t="n">
         <v>-11.7204</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>12.6972</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S27" t="n">
         <v>0.8807999999999999</v>
       </c>
-      <c r="T24" t="n">
-        <v>-4.992100000000001</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="T27" t="n">
+        <v>-4.992099999999999</v>
+      </c>
+      <c r="U27" t="n">
         <v>5.8725</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V27" t="n">
         <v>-7.9731</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W27" t="n">
         <v>0.8347</v>
       </c>
-      <c r="X24" t="n">
-        <v>-8.807599999999999</v>
-      </c>
+      <c r="X27" t="n">
+        <v>-8.807600000000001</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
